--- a/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\정원돈\localhub\localhub\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8A49524-427F-402E-95CB-6EDFC411CF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2BD37B5-647E-43D1-889A-42BE421BCA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -6886,9 +6886,6 @@
     <t>II-2, III-1</t>
   </si>
   <si>
-    <t>먼저 권역을 선정하고 JSON 구조를 파악해야 이후 기능 구현이 수월함</t>
-  </si>
-  <si>
     <t>게시판 기능</t>
   </si>
   <si>
@@ -7883,10 +7880,6 @@
   </si>
   <si>
     <t>보류</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>부산</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
@@ -7957,26 +7950,305 @@
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부산의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원가입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(CRUD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
         <charset val="129"/>
       </rPr>
       <t>관광</t>
@@ -7988,14 +8260,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
         <charset val="129"/>
       </rPr>
       <t>맛집</t>
@@ -8014,156 +8286,346 @@
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여러</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공공데이터와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사이트에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>흩어져</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있고, 광고성 리뷰가 많아서 진실된 리뷰를 찾기 힘들다</t>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>핵심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> UI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
     </r>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공된</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> JSON </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>데이터를</t>
+      <t xml:space="preserve">Netlify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Git Repository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기능명세서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, WBS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>산출물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제출</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>OpenAI API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
     </r>
     <r>
       <rPr>
@@ -8201,6 +8663,431 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
+      <t>후기의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문체와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표현을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>광고성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>또는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후기일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용자에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클릭하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(title), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(addr1), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(firstimage)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
       <t>관광지와</t>
     </r>
     <r>
@@ -8209,158 +9096,107 @@
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
         <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(title), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(addr1), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(firstimage) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구분하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8380,6 +9216,7 @@
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8399,6 +9236,7 @@
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -8418,18 +9256,19 @@
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
         <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제공</t>
     </r>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -8461,83 +9300,121 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후기를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등록</t>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로그인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>익명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>커뮤니티를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목표로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서비스이며</t>
     </r>
     <r>
       <rPr>
@@ -8556,606 +9433,64 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>조회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>삭제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(CRUD)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>게시판</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>OpenAI API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>활용하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>축제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지역</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자연어로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안내하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>챗봇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>메인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>게시판</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>챗봇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
+      <t>제한된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
     </r>
     <r>
       <rPr>
@@ -9183,1280 +9518,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> UI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Netlify </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배포</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, Git Repository </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능명세서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, WBS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>산출물</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제출</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Kakao Maps API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>활용하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> JSON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> mapx, mapy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>좌표를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기반으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광지와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위치를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마커로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표시</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>OpenAI API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>활용하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후기의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>문체와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표현을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분석하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>광고성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>리뷰일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가능성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>또는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후기일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가능성을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용자에게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마커를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>클릭하면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(title), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(addr1), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(firstimage)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>팝업으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표시</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광지와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구분하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>원하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조회할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원가입</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로그인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>익명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>커뮤니티를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목표로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서비스이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제한된</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>핵심</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -10506,323 +9567,6 @@
         <charset val="129"/>
       </rPr>
       <t>집중하기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제외</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>외</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다른</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지역</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	MVP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>권역만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>범위를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최소화하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서비스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>완성도를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>높이기</t>
     </r>
     <r>
       <rPr>
@@ -12421,6 +11165,1434 @@
   </si>
   <si>
     <t>광고성 리뷰인지, AI작성 리뷰인지 판별</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전_충청권</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대전의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공공데이터와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사이트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흩어져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있고, 광고성 리뷰가 많아서 진실된 리뷰를 찾기 힘들다</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제공된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> JSON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>활용하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광지와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(title), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(addr1), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(firstimage) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조회할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>OpenAI API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>활용하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>축제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자연어로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	MVP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>권역만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제공하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>범위를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최소화하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서비스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완성도를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높이기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Kakao Maps API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>활용하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> JSON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> mapx, mapy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좌표를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기반으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광지와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위치를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>권역을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> JSON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파악해야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수월함</t>
+    </r>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -12964,7 +13136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -13059,6 +13231,31 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -13105,11 +13302,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -13122,6 +13325,60 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -13138,104 +13395,60 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -13522,10 +13735,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="40"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -13560,10 +13773,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="37"/>
+      <c r="C9" s="46"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -13614,28 +13827,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="39"/>
+      <c r="C17" s="48"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="42"/>
+      <c r="C18" s="51"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="35"/>
+      <c r="C19" s="44"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="35"/>
+      <c r="C20" s="44"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -13669,13 +13882,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -13767,46 +13980,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="37"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13839,22 +14052,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="37"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -13895,8 +14108,8 @@
       <c r="E6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>150</v>
+      <c r="F6" s="14" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
@@ -13904,16 +14117,16 @@
         <v>146</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
@@ -13921,16 +14134,16 @@
         <v>146</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1">
@@ -13938,16 +14151,16 @@
         <v>146</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
@@ -13955,101 +14168,101 @@
         <v>146</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
       <c r="B11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
       <c r="B12" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
       <c r="B13" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
       <c r="B15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
@@ -14135,37 +14348,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="37"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="46"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="37"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="46"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -14191,11 +14404,11 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>188</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>189</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
@@ -14209,16 +14422,16 @@
       <c r="G6" s="5">
         <v>40</v>
       </c>
-      <c r="H6" s="72" t="s">
-        <v>202</v>
+      <c r="H6" s="38" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>190</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>191</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
@@ -14233,15 +14446,15 @@
         <v>40</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B8" s="69" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>248</v>
+      <c r="B8" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="D8" s="5">
         <v>2</v>
@@ -14255,16 +14468,16 @@
       <c r="G8" s="5">
         <v>32</v>
       </c>
-      <c r="H8" s="73" t="s">
-        <v>204</v>
+      <c r="H8" s="39" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -14278,16 +14491,16 @@
       <c r="G9" s="5">
         <v>24</v>
       </c>
-      <c r="H9" s="73" t="s">
-        <v>204</v>
+      <c r="H9" s="39" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>194</v>
-      </c>
-      <c r="C10" s="70" t="s">
-        <v>195</v>
       </c>
       <c r="D10" s="5">
         <v>3</v>
@@ -14301,16 +14514,16 @@
       <c r="G10" s="5">
         <v>18</v>
       </c>
-      <c r="H10" s="73" t="s">
-        <v>203</v>
+      <c r="H10" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="2:8" s="26" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D11" s="5">
         <v>3</v>
@@ -14324,16 +14537,16 @@
       <c r="G11" s="5">
         <v>18</v>
       </c>
-      <c r="H11" s="73" t="s">
-        <v>203</v>
+      <c r="H11" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="2:8" s="26" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="D12" s="5">
         <v>4</v>
@@ -14347,16 +14560,16 @@
       <c r="G12" s="5">
         <v>12</v>
       </c>
-      <c r="H12" s="73" t="s">
-        <v>203</v>
+      <c r="H12" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>200</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>201</v>
       </c>
       <c r="D13" s="5">
         <v>5</v>
@@ -14370,22 +14583,22 @@
       <c r="G13" s="5">
         <v>10</v>
       </c>
-      <c r="H13" s="73" t="s">
-        <v>203</v>
+      <c r="H13" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="118.7" customHeight="1">
       <c r="B15" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="74" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="76"/>
+      <c r="C15" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -14396,7 +14609,7 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="G6:G13">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14430,23 +14643,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="77"/>
+      <c r="C2" s="74"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="79"/>
+      <c r="C3" s="73"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1">
@@ -14454,7 +14667,7 @@
         <v>45</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1">
@@ -14462,7 +14675,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1">
@@ -14470,110 +14683,101 @@
         <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="53"/>
+      <c r="C9" s="71"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="80" t="s">
-        <v>210</v>
-      </c>
-      <c r="C10" s="42"/>
+      <c r="B10" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="51"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="42"/>
+      <c r="B11" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="51"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="42"/>
+      <c r="B12" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" s="51"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="80" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="42"/>
+      <c r="B13" s="64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="51"/>
     </row>
-    <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="42"/>
+    <row r="14" spans="2:3" s="34" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B14" s="64" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="69"/>
     </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="56" t="s">
+    <row r="15" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B15" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="51"/>
+    </row>
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="57"/>
-    </row>
-    <row r="17" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B17" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="C17" s="42"/>
+      <c r="C17" s="68"/>
     </row>
     <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="42"/>
+      <c r="B18" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="51"/>
     </row>
     <row r="19" spans="2:3" s="26" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B19" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="C19" s="81"/>
+      <c r="B19" s="64" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="69"/>
     </row>
     <row r="20" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B20" s="80" t="s">
-        <v>217</v>
-      </c>
-      <c r="C20" s="42"/>
+      <c r="B20" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" s="51"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="55"/>
+      <c r="C22" s="66"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="C23" s="42"/>
+      <c r="B23" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="C23" s="51"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="80" t="s">
-        <v>220</v>
-      </c>
-      <c r="C24" s="42"/>
+      <c r="B24" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="C24" s="51"/>
     </row>
     <row r="25" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B25" s="80" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="42"/>
+      <c r="B25" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
@@ -14582,6 +14786,15 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14611,73 +14824,73 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="37"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="46"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="82" t="s">
-        <v>222</v>
-      </c>
-      <c r="G4" s="82" t="s">
-        <v>223</v>
-      </c>
-      <c r="H4" s="83" t="s">
+      <c r="F4" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="41" t="s">
         <v>56</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="J4" s="82" t="s">
+        <v>217</v>
+      </c>
+      <c r="J4" s="40" t="s">
         <v>57</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="30" customHeight="1">
@@ -14688,10 +14901,10 @@
         <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="71" t="s">
-        <v>229</v>
+        <v>221</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="F5" s="5">
         <v>1</v>
@@ -14705,10 +14918,10 @@
       <c r="I5" s="5">
         <v>0</v>
       </c>
-      <c r="J5" s="71" t="s">
-        <v>230</v>
-      </c>
-      <c r="K5" s="91"/>
+      <c r="J5" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="K5" s="42"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -14719,11 +14932,11 @@
       <c r="C6" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" s="71" t="s">
-        <v>229</v>
+      <c r="D6" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -14737,10 +14950,10 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="71" t="s">
-        <v>230</v>
-      </c>
-      <c r="K6" s="91"/>
+      <c r="J6" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="K6" s="42"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -14751,11 +14964,11 @@
       <c r="C7" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="70" t="s">
-        <v>232</v>
+      <c r="D7" s="36" t="s">
+        <v>225</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -14769,10 +14982,10 @@
       <c r="I7" s="5">
         <v>0</v>
       </c>
-      <c r="J7" s="71" t="s">
-        <v>230</v>
-      </c>
-      <c r="K7" s="91"/>
+      <c r="J7" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="K7" s="42"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -14784,10 +14997,10 @@
         <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -14801,11 +15014,11 @@
       <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="J8" s="71" t="s">
-        <v>230</v>
-      </c>
-      <c r="K8" s="91"/>
-      <c r="L8" s="3"/>
+      <c r="J8" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="42"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="2:13" ht="30" customHeight="1">
@@ -14815,11 +15028,11 @@
       <c r="C9" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="70" t="s">
-        <v>236</v>
+      <c r="D9" s="36" t="s">
+        <v>229</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -14833,11 +15046,11 @@
       <c r="I9" s="5">
         <v>0</v>
       </c>
-      <c r="J9" s="71" t="s">
-        <v>230</v>
+      <c r="J9" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="91"/>
+      <c r="L9" s="42"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="2:13" ht="30" customHeight="1">
@@ -14847,11 +15060,11 @@
       <c r="C10" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="70" t="s">
-        <v>237</v>
+      <c r="D10" s="36" t="s">
+        <v>230</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F10" s="5">
         <v>2</v>
@@ -14865,11 +15078,11 @@
       <c r="I10" s="5">
         <v>0</v>
       </c>
-      <c r="J10" s="71" t="s">
-        <v>230</v>
+      <c r="J10" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="91"/>
+      <c r="L10" s="42"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="30" customHeight="1">
@@ -14880,10 +15093,10 @@
         <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -14897,11 +15110,11 @@
       <c r="I11" s="5">
         <v>0</v>
       </c>
-      <c r="J11" s="71" t="s">
-        <v>230</v>
+      <c r="J11" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="91"/>
+      <c r="L11" s="42"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
@@ -14911,11 +15124,11 @@
       <c r="C12" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="70" t="s">
-        <v>239</v>
+      <c r="D12" s="36" t="s">
+        <v>232</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F12" s="5">
         <v>2</v>
@@ -14929,11 +15142,11 @@
       <c r="I12" s="5">
         <v>0</v>
       </c>
-      <c r="J12" s="71" t="s">
-        <v>230</v>
+      <c r="J12" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="91"/>
+      <c r="L12" s="42"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
@@ -14944,10 +15157,10 @@
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F13" s="5">
         <v>2</v>
@@ -14961,12 +15174,12 @@
       <c r="I13" s="5">
         <v>0</v>
       </c>
-      <c r="J13" s="71" t="s">
-        <v>230</v>
+      <c r="J13" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:13" ht="30" customHeight="1">
       <c r="B14" s="5">
@@ -14975,11 +15188,11 @@
       <c r="C14" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="70" t="s">
-        <v>241</v>
-      </c>
-      <c r="E14" s="71" t="s">
-        <v>229</v>
+      <c r="D14" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="F14" s="5">
         <v>3</v>
@@ -14993,12 +15206,12 @@
       <c r="I14" s="5">
         <v>0</v>
       </c>
-      <c r="J14" s="71" t="s">
-        <v>230</v>
+      <c r="J14" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="91"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:13" ht="30" customHeight="1">
       <c r="B15" s="5">
@@ -15008,10 +15221,10 @@
         <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F15" s="5">
         <v>3</v>
@@ -15025,12 +15238,12 @@
       <c r="I15" s="5">
         <v>0</v>
       </c>
-      <c r="J15" s="71" t="s">
-        <v>230</v>
+      <c r="J15" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="91"/>
+      <c r="M15" s="42"/>
     </row>
     <row r="16" spans="2:13" ht="30" customHeight="1">
       <c r="B16" s="5">
@@ -15039,11 +15252,11 @@
       <c r="C16" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="E16" s="71" t="s">
-        <v>229</v>
+      <c r="D16" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="F16" s="5">
         <v>3</v>
@@ -15057,12 +15270,12 @@
       <c r="I16" s="5">
         <v>0</v>
       </c>
-      <c r="J16" s="71" t="s">
-        <v>230</v>
+      <c r="J16" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="91"/>
+      <c r="M16" s="42"/>
     </row>
     <row r="17" spans="2:13" ht="30" customHeight="1">
       <c r="B17" s="5">
@@ -15071,11 +15284,11 @@
       <c r="C17" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="70" t="s">
-        <v>244</v>
-      </c>
-      <c r="E17" s="71" t="s">
-        <v>229</v>
+      <c r="D17" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="F17" s="5">
         <v>3</v>
@@ -15089,12 +15302,12 @@
       <c r="I17" s="5">
         <v>0</v>
       </c>
-      <c r="J17" s="71" t="s">
-        <v>230</v>
+      <c r="J17" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="91"/>
+      <c r="M17" s="42"/>
     </row>
     <row r="18" spans="2:13" ht="30" customHeight="1">
       <c r="B18" s="5">
@@ -15103,11 +15316,11 @@
       <c r="C18" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" s="71" t="s">
-        <v>229</v>
+      <c r="D18" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="F18" s="5">
         <v>3</v>
@@ -15121,85 +15334,100 @@
       <c r="I18" s="5">
         <v>0</v>
       </c>
-      <c r="J18" s="71" t="s">
-        <v>230</v>
+      <c r="J18" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="91"/>
+      <c r="M18" s="42"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="60" t="s">
+      <c r="B20" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="90"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="85"/>
+      <c r="C21" s="92"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="84"/>
+      <c r="C22" s="94"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="86"/>
+      <c r="C23" s="78"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="65" t="s">
+      <c r="B24" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="87"/>
+      <c r="C24" s="80"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="90"/>
+      <c r="C25" s="82"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="89"/>
+      <c r="C26" s="84"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="88"/>
+      <c r="C27" s="86"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="92" t="s">
-        <v>246</v>
-      </c>
-      <c r="C28" s="93"/>
+      <c r="B28" s="75" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="K14:L18 L5:M8 K9:K13 M9:M12">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="K15:L18 L5:M7 M8:M12 K9:K14">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>AND(K$4&gt;=$F8,K$4&lt;=$G8)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M13">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(M$4&gt;=$F13,M$4&lt;=$G13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M14">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(M$4&gt;=$F14,M$4&lt;=$G14)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -15231,16 +15459,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="46"/>
+      <c r="C2" s="55"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="37"/>
+      <c r="C3" s="46"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
@@ -15417,6 +15645,6 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\정원돈\localhub\localhub\산출물\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\정원돈\LocalHub\localhub\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2BD37B5-647E-43D1-889A-42BE421BCA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B49CB22-2E8D-4F8F-A3D3-C3CF95917BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9585" yWindow="390" windowWidth="14085" windowHeight="13935" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -7024,106 +7024,6 @@
   </si>
   <si>
     <r>
-      <t>관광지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표시하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>권역별로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>게시글</t>
     </r>
     <r>
@@ -8206,266 +8106,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>메인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>게시판</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>챗봇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>핵심</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> UI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Netlify </t>
     </r>
     <r>
@@ -10182,7 +9822,7 @@
   </si>
   <si>
     <r>
-      <t>부산</t>
+      <t>화면</t>
     </r>
     <r>
       <rPr>
@@ -10191,7 +9831,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">(UI) </t>
     </r>
     <r>
       <rPr>
@@ -10201,7 +9841,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>권역</t>
+      <t>및</t>
     </r>
     <r>
       <rPr>
@@ -10220,7 +9860,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>선정</t>
+      <t>페이지</t>
     </r>
     <r>
       <rPr>
@@ -10239,6 +9879,81 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설계</t>
+    </r>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">JSON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>및</t>
     </r>
     <r>
@@ -10248,7 +9963,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> MVP </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -10258,12 +9973,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>화면</t>
+      <t>기능</t>
     </r>
     <r>
       <rPr>
@@ -10272,7 +9982,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">(UI) </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -10282,262 +9992,11 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구조</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
       <t>설계</t>
     </r>
   </si>
   <si>
-    <t>FE</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">JSON </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구조</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설계</t>
-    </r>
-  </si>
-  <si>
     <t>BE</t>
-  </si>
-  <si>
-    <r>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
   </si>
   <si>
     <r>
@@ -12592,6 +12051,506 @@
         <charset val="129"/>
       </rPr>
       <t>수월함</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>맛집을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>권역별로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조회</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>핵심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> UI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대전 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>권역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MVP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정의</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대전 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
     </r>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -13136,7 +13095,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -13311,7 +13270,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13326,23 +13303,29 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13380,51 +13363,14 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -14109,7 +14055,7 @@
         <v>149</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
@@ -14408,7 +14354,7 @@
         <v>187</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
@@ -14423,15 +14369,15 @@
         <v>40</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
       <c r="B7" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>189</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>190</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
@@ -14446,15 +14392,15 @@
         <v>40</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
       <c r="B8" s="35" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D8" s="5">
         <v>2</v>
@@ -14469,15 +14415,15 @@
         <v>32</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
       <c r="B9" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -14492,15 +14438,15 @@
         <v>24</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
       <c r="B10" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>193</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>194</v>
       </c>
       <c r="D10" s="5">
         <v>3</v>
@@ -14515,15 +14461,15 @@
         <v>18</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="2:8" s="26" customFormat="1" ht="33.75" customHeight="1">
       <c r="B11" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="D11" s="5">
         <v>3</v>
@@ -14538,15 +14484,15 @@
         <v>18</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="2:8" s="26" customFormat="1" ht="33.75" customHeight="1">
       <c r="B12" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="D12" s="5">
         <v>4</v>
@@ -14561,15 +14507,15 @@
         <v>12</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
       <c r="B13" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>199</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>200</v>
       </c>
       <c r="D13" s="5">
         <v>5</v>
@@ -14584,7 +14530,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="118.7" customHeight="1">
@@ -14592,7 +14538,7 @@
         <v>132</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D15" s="62"/>
       <c r="E15" s="62"/>
@@ -14609,7 +14555,7 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="G6:G13">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14643,23 +14589,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="74"/>
+      <c r="C2" s="69"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="73"/>
+      <c r="C3" s="68"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1">
@@ -14667,7 +14613,7 @@
         <v>45</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1">
@@ -14675,7 +14621,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1">
@@ -14683,101 +14629,109 @@
         <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="65"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="64" t="s">
-        <v>244</v>
+      <c r="B10" s="66" t="s">
+        <v>240</v>
       </c>
       <c r="C10" s="51"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="64" t="s">
-        <v>207</v>
+      <c r="B11" s="66" t="s">
+        <v>206</v>
       </c>
       <c r="C11" s="51"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
       <c r="B12" s="50" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C12" s="51"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="64" t="s">
-        <v>208</v>
+      <c r="B13" s="66" t="s">
+        <v>246</v>
       </c>
       <c r="C13" s="51"/>
     </row>
     <row r="14" spans="2:3" s="34" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B14" s="64" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="69"/>
+      <c r="B14" s="66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="70"/>
     </row>
     <row r="15" spans="2:3" ht="25.5" customHeight="1">
       <c r="B15" s="50" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C15" s="51"/>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="68"/>
+      <c r="C17" s="74"/>
     </row>
     <row r="18" spans="2:3" ht="25.5" customHeight="1">
       <c r="B18" s="50" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C18" s="51"/>
     </row>
     <row r="19" spans="2:3" s="26" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B19" s="64" t="s">
-        <v>212</v>
-      </c>
-      <c r="C19" s="69"/>
+      <c r="B19" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="70"/>
     </row>
     <row r="20" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B20" s="64" t="s">
-        <v>211</v>
+      <c r="B20" s="66" t="s">
+        <v>209</v>
       </c>
       <c r="C20" s="51"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="65" t="s">
+      <c r="B22" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="66"/>
+      <c r="C22" s="72"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="64" t="s">
-        <v>213</v>
+      <c r="B23" s="66" t="s">
+        <v>211</v>
       </c>
       <c r="C23" s="51"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="64" t="s">
-        <v>246</v>
+      <c r="B24" s="66" t="s">
+        <v>242</v>
       </c>
       <c r="C24" s="51"/>
     </row>
     <row r="25" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B25" s="64" t="s">
-        <v>214</v>
+      <c r="B25" s="66" t="s">
+        <v>212</v>
       </c>
       <c r="C25" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
@@ -14787,14 +14741,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14824,7 +14770,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="76" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="55"/>
@@ -14840,7 +14786,7 @@
       <c r="M2" s="55"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="75" t="s">
         <v>134</v>
       </c>
       <c r="C3" s="53"/>
@@ -14869,28 +14815,28 @@
         <v>55</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H4" s="41" t="s">
         <v>56</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J4" s="40" t="s">
         <v>57</v>
       </c>
       <c r="K4" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="M4" s="18" t="s">
         <v>218</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="30" customHeight="1">
@@ -14901,10 +14847,10 @@
         <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F5" s="5">
         <v>1</v>
@@ -14919,7 +14865,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K5" s="42"/>
       <c r="L5" s="3"/>
@@ -14932,11 +14878,11 @@
       <c r="C6" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>224</v>
+      <c r="D6" s="95" t="s">
+        <v>247</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -14951,7 +14897,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K6" s="42"/>
       <c r="L6" s="3"/>
@@ -14965,10 +14911,10 @@
         <v>59</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -14983,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K7" s="42"/>
       <c r="L7" s="3"/>
@@ -14997,10 +14943,10 @@
         <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -15015,7 +14961,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="42"/>
@@ -15028,11 +14974,11 @@
       <c r="C9" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="36" t="s">
-        <v>229</v>
+      <c r="D9" s="95" t="s">
+        <v>248</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -15047,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="42"/>
@@ -15061,10 +15007,10 @@
         <v>60</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F10" s="5">
         <v>2</v>
@@ -15079,7 +15025,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="42"/>
@@ -15093,10 +15039,10 @@
         <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -15111,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="42"/>
@@ -15125,10 +15071,10 @@
         <v>60</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F12" s="5">
         <v>2</v>
@@ -15143,7 +15089,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="42"/>
@@ -15157,10 +15103,10 @@
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F13" s="5">
         <v>2</v>
@@ -15175,7 +15121,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="42"/>
@@ -15189,10 +15135,10 @@
         <v>60</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F14" s="5">
         <v>3</v>
@@ -15207,7 +15153,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="42"/>
@@ -15221,10 +15167,10 @@
         <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F15" s="5">
         <v>3</v>
@@ -15239,7 +15185,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -15253,10 +15199,10 @@
         <v>62</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F16" s="5">
         <v>3</v>
@@ -15271,7 +15217,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -15285,10 +15231,10 @@
         <v>63</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F17" s="5">
         <v>3</v>
@@ -15303,7 +15249,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -15317,10 +15263,10 @@
         <v>64</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F18" s="5">
         <v>3</v>
@@ -15335,88 +15281,88 @@
         <v>0</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="42"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="89" t="s">
+      <c r="B20" s="77" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="90"/>
+      <c r="C20" s="78"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="92"/>
+      <c r="C21" s="80"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="94"/>
+      <c r="C22" s="82"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="77" t="s">
+      <c r="B23" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="78"/>
+      <c r="C23" s="86"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="80"/>
+      <c r="C24" s="88"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="82"/>
+      <c r="C25" s="90"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="84"/>
+      <c r="C26" s="92"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="86"/>
+      <c r="C27" s="94"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="75" t="s">
-        <v>239</v>
-      </c>
-      <c r="C28" s="76"/>
+      <c r="B28" s="83" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="K15:L18 L5:M7 M8:M12 K9:K14">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>AND(K$4&gt;=$F8,K$4&lt;=$G8)</formula>
     </cfRule>
   </conditionalFormatting>
